--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/55.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/55.xlsx
@@ -426,13 +426,13 @@
         <v>-16.42283114403533</v>
       </c>
       <c r="E2">
-        <v>-15.61893882549835</v>
+        <v>-15.14585482990978</v>
       </c>
       <c r="F2">
-        <v>2.388939374462223</v>
+        <v>1.527387573506569</v>
       </c>
       <c r="G2">
-        <v>-12.71058702829814</v>
+        <v>-14.01068953589763</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.91960457284283</v>
       </c>
       <c r="E3">
-        <v>-16.08303111856866</v>
+        <v>-16.55110218808816</v>
       </c>
       <c r="F3">
-        <v>2.329171009615433</v>
+        <v>1.591614211715226</v>
       </c>
       <c r="G3">
-        <v>-13.93737199554539</v>
+        <v>-13.71429953470231</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.21853460080452</v>
       </c>
       <c r="E4">
-        <v>-17.30061146982334</v>
+        <v>-16.18361359043336</v>
       </c>
       <c r="F4">
-        <v>2.872848416890416</v>
+        <v>1.527808384147191</v>
       </c>
       <c r="G4">
-        <v>-12.98786507371422</v>
+        <v>-13.50049260641308</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.36203413820342</v>
       </c>
       <c r="E5">
-        <v>-18.19823257382456</v>
+        <v>-17.26383478354199</v>
       </c>
       <c r="F5">
-        <v>2.416149586909381</v>
+        <v>1.675393634099562</v>
       </c>
       <c r="G5">
-        <v>-12.85521314103975</v>
+        <v>-13.54818177248666</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.36885238810323</v>
       </c>
       <c r="E6">
-        <v>-16.99442842453433</v>
+        <v>-18.3790467820623</v>
       </c>
       <c r="F6">
-        <v>2.580790921685394</v>
+        <v>2.126375072266475</v>
       </c>
       <c r="G6">
-        <v>-12.24478972670237</v>
+        <v>-13.01325456486279</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.27461231121016</v>
       </c>
       <c r="E7">
-        <v>-20.60793409091273</v>
+        <v>-18.24410063969597</v>
       </c>
       <c r="F7">
-        <v>2.173910107308722</v>
+        <v>1.892820196516765</v>
       </c>
       <c r="G7">
-        <v>-12.25993857219231</v>
+        <v>-13.29061484873349</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.0894260591255</v>
       </c>
       <c r="E8">
-        <v>-20.25369839059546</v>
+        <v>-18.22235442519917</v>
       </c>
       <c r="F8">
-        <v>2.138051739176337</v>
+        <v>2.279548488718131</v>
       </c>
       <c r="G8">
-        <v>-11.83012907941274</v>
+        <v>-12.43545501493597</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.855038976016834</v>
       </c>
       <c r="E9">
-        <v>-19.6598597757375</v>
+        <v>-19.72022670234388</v>
       </c>
       <c r="F9">
-        <v>2.635034075955511</v>
+        <v>2.010377128117654</v>
       </c>
       <c r="G9">
-        <v>-10.54469895641531</v>
+        <v>-11.75680762294362</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.583326294971146</v>
       </c>
       <c r="E10">
-        <v>-20.61016851860549</v>
+        <v>-20.49592198148211</v>
       </c>
       <c r="F10">
-        <v>2.781507656853325</v>
+        <v>2.217858311496847</v>
       </c>
       <c r="G10">
-        <v>-10.42406428109374</v>
+        <v>-11.52717827705995</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.306576750784409</v>
       </c>
       <c r="E11">
-        <v>-19.97861459170676</v>
+        <v>-20.88489929453158</v>
       </c>
       <c r="F11">
-        <v>3.307993127050607</v>
+        <v>2.441850513948638</v>
       </c>
       <c r="G11">
-        <v>-9.467326902117479</v>
+        <v>-10.86930588515138</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.053987586902651</v>
       </c>
       <c r="E12">
-        <v>-20.51754775285049</v>
+        <v>-21.65474685212444</v>
       </c>
       <c r="F12">
-        <v>3.187167457678271</v>
+        <v>2.365919044338425</v>
       </c>
       <c r="G12">
-        <v>-9.063639214344292</v>
+        <v>-10.36446359282322</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.843044909965692</v>
       </c>
       <c r="E13">
-        <v>-23.86034710507656</v>
+        <v>-23.30576879687221</v>
       </c>
       <c r="F13">
-        <v>2.981626310756436</v>
+        <v>2.694616886504074</v>
       </c>
       <c r="G13">
-        <v>-8.758653336582732</v>
+        <v>-9.667368679550057</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.712024712350655</v>
       </c>
       <c r="E14">
-        <v>-22.07028810480751</v>
+        <v>-24.13890714184414</v>
       </c>
       <c r="F14">
-        <v>3.172937762432981</v>
+        <v>2.880437919034865</v>
       </c>
       <c r="G14">
-        <v>-7.888612258615866</v>
+        <v>-8.62444931624885</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.669013169673729</v>
       </c>
       <c r="E15">
-        <v>-24.59935291537125</v>
+        <v>-24.56783004141581</v>
       </c>
       <c r="F15">
-        <v>2.839702123634796</v>
+        <v>2.883908778452595</v>
       </c>
       <c r="G15">
-        <v>-7.37053479658305</v>
+        <v>-8.018650835954627</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.729044550793261</v>
       </c>
       <c r="E16">
-        <v>-25.41016774947223</v>
+        <v>-25.5708970277431</v>
       </c>
       <c r="F16">
-        <v>3.898262887263451</v>
+        <v>2.632399867614609</v>
       </c>
       <c r="G16">
-        <v>-7.283074852780755</v>
+        <v>-7.207204004218412</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.8969654350577162</v>
       </c>
       <c r="E17">
-        <v>-26.47938708578139</v>
+        <v>-26.44572946120498</v>
       </c>
       <c r="F17">
-        <v>3.487450641193092</v>
+        <v>2.970594113685952</v>
       </c>
       <c r="G17">
-        <v>-6.168456610773805</v>
+        <v>-6.388375292150823</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1629536773814896</v>
       </c>
       <c r="E18">
-        <v>-27.82567545599251</v>
+        <v>-26.94656106165473</v>
       </c>
       <c r="F18">
-        <v>3.490717722229733</v>
+        <v>2.918811210602149</v>
       </c>
       <c r="G18">
-        <v>-5.622006881897065</v>
+        <v>-5.865101143009396</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.468287960405333</v>
       </c>
       <c r="E19">
-        <v>-27.47510704127506</v>
+        <v>-27.74746218032334</v>
       </c>
       <c r="F19">
-        <v>3.349449602091111</v>
+        <v>3.274000242309327</v>
       </c>
       <c r="G19">
-        <v>-4.638199997627845</v>
+        <v>-5.295191263236912</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.008441891293399</v>
       </c>
       <c r="E20">
-        <v>-28.36054677646056</v>
+        <v>-29.16902335258565</v>
       </c>
       <c r="F20">
-        <v>3.804953926277309</v>
+        <v>3.225504301079833</v>
       </c>
       <c r="G20">
-        <v>-4.922648453063411</v>
+        <v>-4.817688688266884</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.458856930050745</v>
       </c>
       <c r="E21">
-        <v>-29.74830911496141</v>
+        <v>-29.38794742794002</v>
       </c>
       <c r="F21">
-        <v>4.267018920293679</v>
+        <v>3.133583683860782</v>
       </c>
       <c r="G21">
-        <v>-4.077654858703685</v>
+        <v>-4.743608810494044</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.818856411400596</v>
       </c>
       <c r="E22">
-        <v>-30.00639381989758</v>
+        <v>-29.66058913856971</v>
       </c>
       <c r="F22">
-        <v>4.008939399216687</v>
+        <v>3.042981827546989</v>
       </c>
       <c r="G22">
-        <v>-3.540575092164451</v>
+        <v>-4.55845480409229</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.091121330334352</v>
       </c>
       <c r="E23">
-        <v>-30.25755096834394</v>
+        <v>-30.24913656219984</v>
       </c>
       <c r="F23">
-        <v>4.302085369188988</v>
+        <v>3.480379697042796</v>
       </c>
       <c r="G23">
-        <v>-3.315521076176712</v>
+        <v>-3.580707458019044</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.267882949285073</v>
       </c>
       <c r="E24">
-        <v>-31.10826570364254</v>
+        <v>-31.14302392922004</v>
       </c>
       <c r="F24">
-        <v>3.523022394204109</v>
+        <v>3.532490633618107</v>
       </c>
       <c r="G24">
-        <v>-3.148994732432552</v>
+        <v>-3.368942132000073</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.34677360649084</v>
       </c>
       <c r="E25">
-        <v>-31.90038901017613</v>
+        <v>-31.72508196015512</v>
       </c>
       <c r="F25">
-        <v>3.723883265300127</v>
+        <v>3.468973077906246</v>
       </c>
       <c r="G25">
-        <v>-2.467689602446447</v>
+        <v>-3.521762066640889</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.324410679629359</v>
       </c>
       <c r="E26">
-        <v>-30.6322246215907</v>
+        <v>-30.86007810129344</v>
       </c>
       <c r="F26">
-        <v>3.948614371475216</v>
+        <v>3.490837007135736</v>
       </c>
       <c r="G26">
-        <v>-3.891887327323019</v>
+        <v>-3.452154394352626</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.196907379002356</v>
       </c>
       <c r="E27">
-        <v>-33.18075553363391</v>
+        <v>-31.40545912301896</v>
       </c>
       <c r="F27">
-        <v>4.064209729066276</v>
+        <v>3.21782202178627</v>
       </c>
       <c r="G27">
-        <v>-4.31079173994551</v>
+        <v>-3.325953611562801</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.967091425774236</v>
       </c>
       <c r="E28">
-        <v>-32.10669770613133</v>
+        <v>-31.872290458958</v>
       </c>
       <c r="F28">
-        <v>4.018821822332085</v>
+        <v>3.441250934404158</v>
       </c>
       <c r="G28">
-        <v>-1.65970070192116</v>
+        <v>-3.106914751112988</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.640845051334366</v>
       </c>
       <c r="E29">
-        <v>-31.82023826142393</v>
+        <v>-31.72458357479614</v>
       </c>
       <c r="F29">
-        <v>3.652289127410971</v>
+        <v>3.222093084115104</v>
       </c>
       <c r="G29">
-        <v>-2.497861977685943</v>
+        <v>-3.078478521026582</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.230166466545116</v>
       </c>
       <c r="E30">
-        <v>-31.6022237393497</v>
+        <v>-31.64112894643504</v>
       </c>
       <c r="F30">
-        <v>3.894631324569578</v>
+        <v>3.203789477982846</v>
       </c>
       <c r="G30">
-        <v>-3.317298993243261</v>
+        <v>-3.757209456845849</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.756198730078397</v>
       </c>
       <c r="E31">
-        <v>-30.785089794218</v>
+        <v>-30.61229959025983</v>
       </c>
       <c r="F31">
-        <v>3.504235021508616</v>
+        <v>3.151994977755404</v>
       </c>
       <c r="G31">
-        <v>-3.675010163394647</v>
+        <v>-3.432513762793681</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2393261582922293</v>
       </c>
       <c r="E32">
-        <v>-29.12561398781855</v>
+        <v>-30.99603970382869</v>
       </c>
       <c r="F32">
-        <v>3.937391649902088</v>
+        <v>3.369206164647879</v>
       </c>
       <c r="G32">
-        <v>-2.598613222201595</v>
+        <v>-3.563682792540395</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2969884830336287</v>
       </c>
       <c r="E33">
-        <v>-31.8225931322451</v>
+        <v>-30.66135316921738</v>
       </c>
       <c r="F33">
-        <v>4.325417165456239</v>
+        <v>3.583812964425953</v>
       </c>
       <c r="G33">
-        <v>-3.181276589301667</v>
+        <v>-3.773101059171956</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.827585815143375</v>
       </c>
       <c r="E34">
-        <v>-29.86140936575914</v>
+        <v>-30.96692569244164</v>
       </c>
       <c r="F34">
-        <v>4.406012343544213</v>
+        <v>3.295928784196235</v>
       </c>
       <c r="G34">
-        <v>-2.71421177120691</v>
+        <v>-3.99584717694115</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.33378644269096</v>
       </c>
       <c r="E35">
-        <v>-30.53887081403686</v>
+        <v>-30.15925899252489</v>
       </c>
       <c r="F35">
-        <v>4.374487993663275</v>
+        <v>3.532013493994094</v>
       </c>
       <c r="G35">
-        <v>-3.250226353952969</v>
+        <v>-4.642285812912938</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.79589826106319</v>
       </c>
       <c r="E36">
-        <v>-29.80072471848641</v>
+        <v>-29.48553543443951</v>
       </c>
       <c r="F36">
-        <v>4.781786305210959</v>
+        <v>3.96385136148231</v>
       </c>
       <c r="G36">
-        <v>-3.330676448528125</v>
+        <v>-4.19752458586006</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.203248570021085</v>
       </c>
       <c r="E37">
-        <v>-29.97684164471577</v>
+        <v>-29.50772188933675</v>
       </c>
       <c r="F37">
-        <v>4.517542073922333</v>
+        <v>4.014184621611213</v>
       </c>
       <c r="G37">
-        <v>-4.13350129625219</v>
+        <v>-4.889985427483992</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.549291001958335</v>
       </c>
       <c r="E38">
-        <v>-27.98559901126636</v>
+        <v>-28.97873151610466</v>
       </c>
       <c r="F38">
-        <v>3.874735596289139</v>
+        <v>3.841513093232462</v>
       </c>
       <c r="G38">
-        <v>-3.693546449991552</v>
+        <v>-4.939746219390612</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.829380089928657</v>
       </c>
       <c r="E39">
-        <v>-28.64901637544917</v>
+        <v>-28.5184705604815</v>
       </c>
       <c r="F39">
-        <v>4.478095218201021</v>
+        <v>4.215999771955257</v>
       </c>
       <c r="G39">
-        <v>-4.612191760011175</v>
+        <v>-4.801773589239457</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.04872996133789</v>
       </c>
       <c r="E40">
-        <v>-28.03512605631494</v>
+        <v>-28.05513830508362</v>
       </c>
       <c r="F40">
-        <v>4.17789487142648</v>
+        <v>4.621800395238679</v>
       </c>
       <c r="G40">
-        <v>-5.355073911923278</v>
+        <v>-5.490443629717093</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.211714759196599</v>
       </c>
       <c r="E41">
-        <v>-27.69328769180228</v>
+        <v>-28.53128529402425</v>
       </c>
       <c r="F41">
-        <v>5.22828461899392</v>
+        <v>4.619949822460825</v>
       </c>
       <c r="G41">
-        <v>-4.721610676569323</v>
+        <v>-5.862832405959718</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.331988752778742</v>
       </c>
       <c r="E42">
-        <v>-27.45679137933256</v>
+        <v>-27.0199399993418</v>
       </c>
       <c r="F42">
-        <v>4.659931803524346</v>
+        <v>4.566465452731672</v>
       </c>
       <c r="G42">
-        <v>-4.657663098554595</v>
+        <v>-5.784799860875934</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.421922631389733</v>
       </c>
       <c r="E43">
-        <v>-27.15897705486308</v>
+        <v>-26.33360106185726</v>
       </c>
       <c r="F43">
-        <v>5.133815943643859</v>
+        <v>4.798873867995907</v>
       </c>
       <c r="G43">
-        <v>-5.252894590116286</v>
+        <v>-6.282666243656646</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.49325865308559</v>
       </c>
       <c r="E44">
-        <v>-25.46001874500415</v>
+        <v>-25.85378886392247</v>
       </c>
       <c r="F44">
-        <v>4.989007381225672</v>
+        <v>4.968082820630956</v>
       </c>
       <c r="G44">
-        <v>-5.479173045317257</v>
+        <v>-6.554682333349331</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.561081990664165</v>
       </c>
       <c r="E45">
-        <v>-24.18583012339205</v>
+        <v>-24.69996445971523</v>
       </c>
       <c r="F45">
-        <v>5.448421599553083</v>
+        <v>4.827460827066518</v>
       </c>
       <c r="G45">
-        <v>-5.780507796768143</v>
+        <v>-6.777381457715885</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.630899297980667</v>
       </c>
       <c r="E46">
-        <v>-23.82610387770335</v>
+        <v>-24.43195773292404</v>
       </c>
       <c r="F46">
-        <v>4.820613542114978</v>
+        <v>5.068151259623942</v>
       </c>
       <c r="G46">
-        <v>-5.968768589233322</v>
+        <v>-6.469830523393558</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.715981086981899</v>
       </c>
       <c r="E47">
-        <v>-25.66350533386412</v>
+        <v>-24.31925619041349</v>
       </c>
       <c r="F47">
-        <v>5.550537762765789</v>
+        <v>5.141554551920812</v>
       </c>
       <c r="G47">
-        <v>-5.910243527734336</v>
+        <v>-6.859022051824589</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.820818622218349</v>
       </c>
       <c r="E48">
-        <v>-23.11908194782117</v>
+        <v>-23.5573163471831</v>
       </c>
       <c r="F48">
-        <v>5.354191494015028</v>
+        <v>5.063711210344937</v>
       </c>
       <c r="G48">
-        <v>-7.011014380430022</v>
+        <v>-7.799903073526723</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.949060610184901</v>
       </c>
       <c r="E49">
-        <v>-22.35347481899095</v>
+        <v>-22.42597327587715</v>
       </c>
       <c r="F49">
-        <v>5.889981186880554</v>
+        <v>5.060044856220146</v>
       </c>
       <c r="G49">
-        <v>-5.740537297078199</v>
+        <v>-6.898339865366754</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.108754252778152</v>
       </c>
       <c r="E50">
-        <v>-22.2068332335339</v>
+        <v>-22.71641980345639</v>
       </c>
       <c r="F50">
-        <v>4.969129877028095</v>
+        <v>5.300824752457073</v>
       </c>
       <c r="G50">
-        <v>-6.122058457900539</v>
+        <v>-7.059837915028432</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.29551729903031</v>
       </c>
       <c r="E51">
-        <v>-20.68770482082871</v>
+        <v>-21.58098166578416</v>
       </c>
       <c r="F51">
-        <v>6.14628965845036</v>
+        <v>5.071912047632652</v>
       </c>
       <c r="G51">
-        <v>-6.530065622599723</v>
+        <v>-7.689281909084367</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.517991716244971</v>
       </c>
       <c r="E52">
-        <v>-21.69856738481271</v>
+        <v>-21.03690267580897</v>
       </c>
       <c r="F52">
-        <v>5.566142547899727</v>
+        <v>5.094839600607337</v>
       </c>
       <c r="G52">
-        <v>-7.288069207183555</v>
+        <v>-7.533163298652679</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.775555363932667</v>
       </c>
       <c r="E53">
-        <v>-19.72238221902147</v>
+        <v>-20.73177454619647</v>
       </c>
       <c r="F53">
-        <v>5.569129640754221</v>
+        <v>5.131143630402428</v>
       </c>
       <c r="G53">
-        <v>-5.51562165055379</v>
+        <v>-7.753202074280889</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.066974873634468</v>
       </c>
       <c r="E54">
-        <v>-21.39603501227822</v>
+        <v>-19.61414122547378</v>
       </c>
       <c r="F54">
-        <v>5.368722714994937</v>
+        <v>5.1851366177169</v>
       </c>
       <c r="G54">
-        <v>-6.997213984521397</v>
+        <v>-7.532964882063754</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.399784705141195</v>
       </c>
       <c r="E55">
-        <v>-18.85495080814043</v>
+        <v>-19.54476598350385</v>
       </c>
       <c r="F55">
-        <v>5.29052648890547</v>
+        <v>5.250842720106957</v>
       </c>
       <c r="G55">
-        <v>-7.202898886387666</v>
+        <v>-7.690585976007628</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.766323688286938</v>
       </c>
       <c r="E56">
-        <v>-20.20702875493836</v>
+        <v>-18.52441748485395</v>
       </c>
       <c r="F56">
-        <v>5.479962516782077</v>
+        <v>5.242582240366239</v>
       </c>
       <c r="G56">
-        <v>-7.725199227796608</v>
+        <v>-8.051461368603444</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.174833583916265</v>
       </c>
       <c r="E57">
-        <v>-18.43217881454083</v>
+        <v>-18.31327237431099</v>
       </c>
       <c r="F57">
-        <v>5.108186256201242</v>
+        <v>5.307960309264788</v>
       </c>
       <c r="G57">
-        <v>-7.336033806811488</v>
+        <v>-7.566421573998871</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.622838114844641</v>
       </c>
       <c r="E58">
-        <v>-18.18697321792295</v>
+        <v>-17.89642701327192</v>
       </c>
       <c r="F58">
-        <v>5.593710615064894</v>
+        <v>5.227963212441634</v>
       </c>
       <c r="G58">
-        <v>-7.47430406184603</v>
+        <v>-8.185337740491143</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.102388585862117</v>
       </c>
       <c r="E59">
-        <v>-18.94681153622298</v>
+        <v>-17.03623880294138</v>
       </c>
       <c r="F59">
-        <v>4.772424096824519</v>
+        <v>5.189351351062344</v>
       </c>
       <c r="G59">
-        <v>-8.310814041656933</v>
+        <v>-7.882828153974255</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.615222604538222</v>
       </c>
       <c r="E60">
-        <v>-15.16923740966856</v>
+        <v>-16.07876577053806</v>
       </c>
       <c r="F60">
-        <v>6.272531193902199</v>
+        <v>5.476218296121424</v>
       </c>
       <c r="G60">
-        <v>-7.901372272804933</v>
+        <v>-8.994306975610392</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.142539234287513</v>
       </c>
       <c r="E61">
-        <v>-16.93259956754161</v>
+        <v>-15.76448396316564</v>
       </c>
       <c r="F61">
-        <v>5.286218978410912</v>
+        <v>5.150027093716646</v>
       </c>
       <c r="G61">
-        <v>-7.521240028105065</v>
+        <v>-8.832508690320736</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.681851623909909</v>
       </c>
       <c r="E62">
-        <v>-15.29801603321752</v>
+        <v>-16.08127431017826</v>
       </c>
       <c r="F62">
-        <v>5.031088445287887</v>
+        <v>5.110240607360185</v>
       </c>
       <c r="G62">
-        <v>-7.839403639190268</v>
+        <v>-8.45652752952074</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.22074816932887</v>
       </c>
       <c r="E63">
-        <v>-16.85154134211493</v>
+        <v>-15.29425737696855</v>
       </c>
       <c r="F63">
-        <v>5.334544275955429</v>
+        <v>4.867648243245933</v>
       </c>
       <c r="G63">
-        <v>-8.555405564792268</v>
+        <v>-9.088718026886525</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.740931205262717</v>
       </c>
       <c r="E64">
-        <v>-15.66159230580433</v>
+        <v>-15.09701721794112</v>
       </c>
       <c r="F64">
-        <v>5.552307155538169</v>
+        <v>5.105699497258038</v>
       </c>
       <c r="G64">
-        <v>-8.97710086338266</v>
+        <v>-8.891544152387286</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.23894105655153</v>
       </c>
       <c r="E65">
-        <v>-15.82457677782458</v>
+        <v>-13.78373441812841</v>
       </c>
       <c r="F65">
-        <v>5.488744867986558</v>
+        <v>4.845862180552306</v>
       </c>
       <c r="G65">
-        <v>-9.325777551876499</v>
+        <v>-9.312915718648378</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.69229333953059</v>
       </c>
       <c r="E66">
-        <v>-15.90755794009466</v>
+        <v>-14.629245179637</v>
       </c>
       <c r="F66">
-        <v>5.010357722665426</v>
+        <v>4.651765757667548</v>
       </c>
       <c r="G66">
-        <v>-8.497961351554002</v>
+        <v>-9.113439167419777</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.09857443395421</v>
       </c>
       <c r="E67">
-        <v>-14.85623894459551</v>
+        <v>-13.36817239938871</v>
       </c>
       <c r="F67">
-        <v>5.30727442105527</v>
+        <v>4.27807099818183</v>
       </c>
       <c r="G67">
-        <v>-8.890794868689637</v>
+        <v>-9.310106557468341</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.44879753855758</v>
       </c>
       <c r="E68">
-        <v>-14.38925601644311</v>
+        <v>-14.1612239486534</v>
       </c>
       <c r="F68">
-        <v>4.611657864758802</v>
+        <v>4.55965627268066</v>
       </c>
       <c r="G68">
-        <v>-9.528142891995167</v>
+        <v>-9.281218668567673</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.73063265482295</v>
       </c>
       <c r="E69">
-        <v>-12.32374358147746</v>
+        <v>-13.62568811437338</v>
       </c>
       <c r="F69">
-        <v>4.925615737359037</v>
+        <v>4.786352266335189</v>
       </c>
       <c r="G69">
-        <v>-9.355396449262679</v>
+        <v>-9.116988474691397</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.94975798296396</v>
       </c>
       <c r="E70">
-        <v>-13.53048820438566</v>
+        <v>-13.69762588773074</v>
       </c>
       <c r="F70">
-        <v>4.228496522593891</v>
+        <v>4.694491291569141</v>
       </c>
       <c r="G70">
-        <v>-8.87153671121329</v>
+        <v>-9.490028631709505</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.09355328031328</v>
       </c>
       <c r="E71">
-        <v>-13.84105704083369</v>
+        <v>-13.08418826863091</v>
       </c>
       <c r="F71">
-        <v>4.303992270950232</v>
+        <v>4.682426948714769</v>
       </c>
       <c r="G71">
-        <v>-8.743740763478295</v>
+        <v>-9.185242475909167</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.17007646177893</v>
       </c>
       <c r="E72">
-        <v>-15.44684636104275</v>
+        <v>-13.7063683975695</v>
       </c>
       <c r="F72">
-        <v>4.929351674345662</v>
+        <v>4.430306702733517</v>
       </c>
       <c r="G72">
-        <v>-8.383895309623671</v>
+        <v>-9.312666392539928</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.18017750314271</v>
       </c>
       <c r="E73">
-        <v>-14.57767060140528</v>
+        <v>-13.4822860337497</v>
       </c>
       <c r="F73">
-        <v>4.186206709946171</v>
+        <v>4.486761597969109</v>
       </c>
       <c r="G73">
-        <v>-7.665462780807345</v>
+        <v>-9.266525398008888</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.12137514303817</v>
       </c>
       <c r="E74">
-        <v>-15.28370822020348</v>
+        <v>-13.79908468718497</v>
       </c>
       <c r="F74">
-        <v>4.751549238273971</v>
+        <v>4.283654194476698</v>
       </c>
       <c r="G74">
-        <v>-8.320230997397079</v>
+        <v>-8.827959467870722</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.00627913413822</v>
       </c>
       <c r="E75">
-        <v>-17.09792645074906</v>
+        <v>-13.55007474899356</v>
       </c>
       <c r="F75">
-        <v>4.543824514878356</v>
+        <v>4.24904334765293</v>
       </c>
       <c r="G75">
-        <v>-7.950835439828165</v>
+        <v>-8.743076328979855</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.82702247975639</v>
       </c>
       <c r="E76">
-        <v>-15.89840426233473</v>
+        <v>-13.85194676092739</v>
       </c>
       <c r="F76">
-        <v>4.012897338667263</v>
+        <v>4.122558272184667</v>
       </c>
       <c r="G76">
-        <v>-8.398515479333906</v>
+        <v>-8.541579061437732</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.59375946215132</v>
       </c>
       <c r="E77">
-        <v>-14.42041340780197</v>
+        <v>-13.67512794198414</v>
       </c>
       <c r="F77">
-        <v>4.495787489190013</v>
+        <v>4.423832183113237</v>
       </c>
       <c r="G77">
-        <v>-7.630126352766626</v>
+        <v>-8.750618770103582</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.30454260468613</v>
       </c>
       <c r="E78">
-        <v>-15.93876932320074</v>
+        <v>-13.18348739819624</v>
       </c>
       <c r="F78">
-        <v>3.864670932345125</v>
+        <v>3.928243160305571</v>
       </c>
       <c r="G78">
-        <v>-7.727658549201436</v>
+        <v>-8.730732728553072</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.95379768494899</v>
       </c>
       <c r="E79">
-        <v>-15.45535629104732</v>
+        <v>-14.99814171593092</v>
       </c>
       <c r="F79">
-        <v>4.065374413634612</v>
+        <v>4.032024341997904</v>
       </c>
       <c r="G79">
-        <v>-7.478570018507909</v>
+        <v>-7.99711610919483</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.5470139607883</v>
       </c>
       <c r="E80">
-        <v>-16.91757324896838</v>
+        <v>-15.18379856857341</v>
       </c>
       <c r="F80">
-        <v>3.789743444027105</v>
+        <v>3.87278893289256</v>
       </c>
       <c r="G80">
-        <v>-7.599669406366699</v>
+        <v>-7.770503478686197</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.07101662517803</v>
       </c>
       <c r="E81">
-        <v>-18.35477541508</v>
+        <v>-15.92655888190574</v>
       </c>
       <c r="F81">
-        <v>4.472604799055266</v>
+        <v>3.862959525290941</v>
       </c>
       <c r="G81">
-        <v>-6.275705998576738</v>
+        <v>-7.678709698862654</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.532244649359978</v>
       </c>
       <c r="E82">
-        <v>-18.06300401308815</v>
+        <v>-15.46024046756532</v>
       </c>
       <c r="F82">
-        <v>3.748846945350893</v>
+        <v>3.789364051756622</v>
       </c>
       <c r="G82">
-        <v>-6.590204124256018</v>
+        <v>-7.475690367223911</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.928725770373868</v>
       </c>
       <c r="E83">
-        <v>-18.10613095948517</v>
+        <v>-17.53802564199584</v>
       </c>
       <c r="F83">
-        <v>3.7338766896475</v>
+        <v>4.064285938867333</v>
       </c>
       <c r="G83">
-        <v>-5.214840376956219</v>
+        <v>-7.092122382642138</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.262406198940328</v>
       </c>
       <c r="E84">
-        <v>-18.86981515147199</v>
+        <v>-17.53099840843423</v>
       </c>
       <c r="F84">
-        <v>4.109059196988647</v>
+        <v>3.846778196444656</v>
       </c>
       <c r="G84">
-        <v>-6.335700909280521</v>
+        <v>-6.486460966438949</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.551383325878885</v>
       </c>
       <c r="E85">
-        <v>-19.41320470836726</v>
+        <v>-19.66459858985913</v>
       </c>
       <c r="F85">
-        <v>3.891051120654678</v>
+        <v>3.608099039941229</v>
       </c>
       <c r="G85">
-        <v>-5.649907909342293</v>
+        <v>-6.215682369682453</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.802924877894244</v>
       </c>
       <c r="E86">
-        <v>-21.50029307616539</v>
+        <v>-19.69453493708849</v>
       </c>
       <c r="F86">
-        <v>3.686190891737944</v>
+        <v>3.777824893835625</v>
       </c>
       <c r="G86">
-        <v>-4.888238839352538</v>
+        <v>-5.785397721387299</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.045849097918071</v>
       </c>
       <c r="E87">
-        <v>-23.39894609294474</v>
+        <v>-20.36295692091772</v>
       </c>
       <c r="F87">
-        <v>3.821534528211744</v>
+        <v>3.689910261376514</v>
       </c>
       <c r="G87">
-        <v>-5.508175806979934</v>
+        <v>-5.649265666172878</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.301998919571849</v>
       </c>
       <c r="E88">
-        <v>-24.68737607618967</v>
+        <v>-22.31708853457412</v>
       </c>
       <c r="F88">
-        <v>3.692993444849733</v>
+        <v>3.448099876090504</v>
       </c>
       <c r="G88">
-        <v>-5.74769073725785</v>
+        <v>-5.504763563799349</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.592467462862838</v>
       </c>
       <c r="E89">
-        <v>-25.29262356255693</v>
+        <v>-23.91690138368675</v>
       </c>
       <c r="F89">
-        <v>3.90662774129692</v>
+        <v>3.210832257641448</v>
       </c>
       <c r="G89">
-        <v>-4.544620468503981</v>
+        <v>-5.131633336092848</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.947798671010539</v>
       </c>
       <c r="E90">
-        <v>-26.8619310744887</v>
+        <v>-24.81309378299223</v>
       </c>
       <c r="F90">
-        <v>4.172308361662</v>
+        <v>3.285378696954181</v>
       </c>
       <c r="G90">
-        <v>-3.318257136508199</v>
+        <v>-4.88493624744478</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.379362201501504</v>
       </c>
       <c r="E91">
-        <v>-27.69231584035226</v>
+        <v>-26.8351677807115</v>
       </c>
       <c r="F91">
-        <v>4.005322747136065</v>
+        <v>3.077647346619343</v>
       </c>
       <c r="G91">
-        <v>-4.324059543957548</v>
+        <v>-5.080528010721805</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.906107462016218</v>
       </c>
       <c r="E92">
-        <v>-29.52471060026096</v>
+        <v>-28.21966777171671</v>
       </c>
       <c r="F92">
-        <v>3.977189733402188</v>
+        <v>3.041404616012059</v>
       </c>
       <c r="G92">
-        <v>-3.863996742856156</v>
+        <v>-4.562974002979507</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.533268471611654</v>
       </c>
       <c r="E93">
-        <v>-28.80335386149113</v>
+        <v>-30.89543854251303</v>
       </c>
       <c r="F93">
-        <v>4.100651267850232</v>
+        <v>2.86356738850945</v>
       </c>
       <c r="G93">
-        <v>-3.508113093918548</v>
+        <v>-4.559480826716597</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.255051008096213</v>
       </c>
       <c r="E94">
-        <v>-32.63151825519328</v>
+        <v>-31.88897390884984</v>
       </c>
       <c r="F94">
-        <v>3.274225558242888</v>
+        <v>2.711210742316954</v>
       </c>
       <c r="G94">
-        <v>-4.753772439187248</v>
+        <v>-4.100585028447433</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.068925754514058</v>
       </c>
       <c r="E95">
-        <v>-33.43186492015003</v>
+        <v>-33.4079984912719</v>
       </c>
       <c r="F95">
-        <v>3.16299238339497</v>
+        <v>2.22407603722226</v>
       </c>
       <c r="G95">
-        <v>-3.518360266438668</v>
+        <v>-4.362562805187287</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.955970956831457</v>
       </c>
       <c r="E96">
-        <v>-37.55427395318798</v>
+        <v>-36.13818879005746</v>
       </c>
       <c r="F96">
-        <v>2.676770539178162</v>
+        <v>2.132566290234998</v>
       </c>
       <c r="G96">
-        <v>-3.361527617361311</v>
+        <v>-3.970648270147725</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.900008419528386</v>
       </c>
       <c r="E97">
-        <v>-38.7910795196653</v>
+        <v>-38.26382518876699</v>
       </c>
       <c r="F97">
-        <v>2.985913940433326</v>
+        <v>1.677628569352315</v>
       </c>
       <c r="G97">
-        <v>-4.134605641214231</v>
+        <v>-4.670766425657392</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.885696430692156</v>
       </c>
       <c r="E98">
-        <v>-42.36702769603327</v>
+        <v>-40.28567698968038</v>
       </c>
       <c r="F98">
-        <v>2.094448135827776</v>
+        <v>1.687862220246501</v>
       </c>
       <c r="G98">
-        <v>-4.704847085549785</v>
+        <v>-4.729461185554801</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.888386362127903</v>
       </c>
       <c r="E99">
-        <v>-43.77664630913104</v>
+        <v>-42.92709031979206</v>
       </c>
       <c r="F99">
-        <v>1.475240188765535</v>
+        <v>1.494852615394216</v>
       </c>
       <c r="G99">
-        <v>-3.599235912382175</v>
+        <v>-4.227981532259988</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.905888651111584</v>
       </c>
       <c r="E100">
-        <v>-46.26656917956394</v>
+        <v>-45.16413868889578</v>
       </c>
       <c r="F100">
-        <v>1.865889972251753</v>
+        <v>0.9148794619981698</v>
       </c>
       <c r="G100">
-        <v>-3.872105715556154</v>
+        <v>-4.969613137512948</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.913145902355381</v>
       </c>
       <c r="E101">
-        <v>-49.28566620283004</v>
+        <v>-47.44140883307481</v>
       </c>
       <c r="F101">
-        <v>1.312964671291917</v>
+        <v>0.9704827955436839</v>
       </c>
       <c r="G101">
-        <v>-4.818605059618364</v>
+        <v>-4.905571572692939</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.927384008160154</v>
       </c>
       <c r="E102">
-        <v>-48.07550867851565</v>
+        <v>-49.82034439897148</v>
       </c>
       <c r="F102">
-        <v>1.098286631917203</v>
+        <v>0.791462659389877</v>
       </c>
       <c r="G102">
-        <v>-5.450608888745887</v>
+        <v>-4.870509272834288</v>
       </c>
     </row>
   </sheetData>
